--- a/PROJECTS/Documents/2. DocumentsGeneration/cfgDependencies.xlsx
+++ b/PROJECTS/Documents/2. DocumentsGeneration/cfgDependencies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\Windows\Projects\Excel\PROJECTS\2. DocumentsGeneration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE5CDF5-847B-4E06-9A63-21214F65386E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597A7488-5983-4732-BF5A-2A95BA841692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF16710E-FAF6-445F-AD75-CD3560A0E894}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="117">
   <si>
     <t>ПІБ</t>
   </si>
@@ -387,6 +387,12 @@
   </si>
   <si>
     <t>полковник</t>
+  </si>
+  <si>
+    <t>tbTickets::column.destination</t>
+  </si>
+  <si>
+    <t>Куди</t>
   </si>
 </sst>
 </file>
@@ -549,7 +555,17 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 4" xfId="1" xr:uid="{98265266-0594-4C2A-BAC9-F7BD39857057}"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -835,14 +851,14 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="TableStyleDark_my" pivot="0" count="8" xr9:uid="{CFC3E1FC-0CEF-4FBB-AEF8-B86D335BF785}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="secondRowStripe" dxfId="10"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="9"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstColumn" dxfId="14"/>
+      <tableStyleElement type="lastColumn" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="secondRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -857,12 +873,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD8EF566-CDD9-4A5B-81D2-EE15B9C2E244}" name="tbConfig" displayName="tbConfig" ref="B2:D59" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD8EF566-CDD9-4A5B-81D2-EE15B9C2E244}" name="tbConfig" displayName="tbConfig" ref="B2:D59" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="B2:D59" xr:uid="{CD8EF566-CDD9-4A5B-81D2-EE15B9C2E244}"/>
   <tableColumns count="3">
-    <tableColumn id="15" xr3:uid="{5CE83962-BE71-4EE8-B302-6ACA6C6BD1D3}" name="Kind" dataDxfId="3" dataCellStyle="Обычный 4"/>
-    <tableColumn id="14" xr3:uid="{BC594DB5-8FF8-4EAB-BE26-6C7DA44BDD80}" name="Key" dataDxfId="2" dataCellStyle="Обычный 4"/>
-    <tableColumn id="12" xr3:uid="{E0498979-BE7D-405E-9485-9E20BF41C4F4}" name="Value" dataDxfId="1" dataCellStyle="Обычный 4"/>
+    <tableColumn id="15" xr3:uid="{5CE83962-BE71-4EE8-B302-6ACA6C6BD1D3}" name="Kind" dataDxfId="4" dataCellStyle="Обычный 4"/>
+    <tableColumn id="14" xr3:uid="{BC594DB5-8FF8-4EAB-BE26-6C7DA44BDD80}" name="Key" dataDxfId="3" dataCellStyle="Обычный 4"/>
+    <tableColumn id="12" xr3:uid="{E0498979-BE7D-405E-9485-9E20BF41C4F4}" name="Value" dataDxfId="2" dataCellStyle="Обычный 4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark_my" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1241,388 +1257,388 @@
       </c>
     </row>
     <row r="6" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="8" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="8" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="8" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="8" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="8" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D20" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+    <row r="21" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C21" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D21" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+    <row r="22" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C22" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D22" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
+    <row r="23" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D23" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
+    <row r="24" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C24" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D24" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+    <row r="25" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C25" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D25" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+    <row r="26" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C26" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D26" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+    <row r="27" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C27" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D27" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
+    <row r="28" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C28" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D28" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+    <row r="29" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C29" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D29" s="8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
+    <row r="30" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C30" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D30" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="4" t="s">
+    <row r="31" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D31" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="4" t="s">
+    <row r="32" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D32" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="4" t="s">
+    <row r="33" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D33" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="4" t="s">
+    <row r="34" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D34" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="4" t="s">
+    <row r="35" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D35" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="4" t="s">
+    <row r="36" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D36" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="4" t="s">
+    <row r="37" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D37" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="4" t="s">
+    <row r="38" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D38" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="3" t="s">
+    <row r="39" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C39" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D39" s="8" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1630,10 +1646,10 @@
         <v>7</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1641,10 +1657,10 @@
         <v>7</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1652,10 +1668,10 @@
         <v>7</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1663,10 +1679,10 @@
         <v>7</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1674,10 +1690,10 @@
         <v>7</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1685,10 +1701,10 @@
         <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1696,10 +1712,10 @@
         <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1707,10 +1723,10 @@
         <v>7</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1718,10 +1734,10 @@
         <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1729,10 +1745,10 @@
         <v>7</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1740,10 +1756,10 @@
         <v>7</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1751,10 +1767,10 @@
         <v>7</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1762,10 +1778,10 @@
         <v>7</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1773,10 +1789,10 @@
         <v>7</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1784,10 +1800,10 @@
         <v>7</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1795,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1806,10 +1822,10 @@
         <v>7</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1817,20 +1833,26 @@
         <v>7</v>
       </c>
       <c r="C58" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D59" s="8" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="59" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="6"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3:C59">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D59" xr:uid="{684FC949-A90B-4D12-9A5A-C8807EBFC490}">
